--- a/Results/descriptive.xlsx
+++ b/Results/descriptive.xlsx
@@ -1,85 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\Documents\__CODE_PROJECTS__\hrs_quality\Results\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665721FD-E8C3-4718-963A-A50454E6FA0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
-  <si>
-    <t>Gender</t>
-  </si>
-  <si>
-    <t>Race</t>
-  </si>
-  <si>
-    <t>Physical</t>
-  </si>
-  <si>
-    <t>Stress</t>
-  </si>
-  <si>
-    <t>Poverty</t>
-  </si>
-  <si>
-    <t>Any</t>
-  </si>
-  <si>
-    <t>All</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>White</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>Black</t>
-  </si>
-  <si>
-    <t>Hispan</t>
-  </si>
-  <si>
-    <t>Healthy worker</t>
-  </si>
-  <si>
-    <t>Unhealthy worker</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-  </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -95,14 +31,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -112,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -120,52 +48,28 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -203,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -237,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -272,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -448,238 +350,286 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Healthy</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Unhealthy</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Stress</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Poverty</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C2">
         <v>0.5339508229492903</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2">
         <v>0.4660491770507097</v>
       </c>
-      <c r="E2" s="2">
-        <v>0.37388673016746332</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0.59959737955507031</v>
-      </c>
-      <c r="G2" s="2">
-        <v>8.2169871047282669E-2</v>
-      </c>
-      <c r="H2" s="2">
-        <v>0.77081316553727008</v>
-      </c>
-      <c r="I2" s="2">
-        <v>2.4443368828654409E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0.60320567722990337</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0.39679432277009669</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0.31781864299302481</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0.63599748269351797</v>
-      </c>
-      <c r="G3" s="2">
-        <v>2.4354424183086521E-2</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0.76120162932790225</v>
-      </c>
-      <c r="I3" s="2">
-        <v>8.6558044806517315E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0.50198135198135196</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0.49801864801864798</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0.28799238367249791</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0.66363206431780564</v>
-      </c>
-      <c r="G4" s="2">
-        <v>3.2987527683879241E-2</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0.76731963688485427</v>
-      </c>
-      <c r="I4" s="2">
-        <v>8.0028666985188721E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0.62269309637730685</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0.37730690362269309</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0.49558459908159658</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0.50157287661656769</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0.10150375939849619</v>
-      </c>
-      <c r="H5" s="2">
-        <v>0.77018413597733715</v>
-      </c>
-      <c r="I5" s="2">
-        <v>2.9390934844192629E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0.44860481755306458</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0.55139518244693542</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0.43360234776228912</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0.55853894533139814</v>
-      </c>
-      <c r="G6" s="2">
+      <c r="E2">
+        <v>0.3738867301674633</v>
+      </c>
+      <c r="F2">
+        <v>0.5995973795550703</v>
+      </c>
+      <c r="G2">
+        <v>0.08216987104728267</v>
+      </c>
+      <c r="H2">
+        <v>0.7708131655372701</v>
+      </c>
+      <c r="I2">
+        <v>0.02444336882865441</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>0.6032056772299034</v>
+      </c>
+      <c r="D3">
+        <v>0.3967943227700967</v>
+      </c>
+      <c r="E3">
+        <v>0.3178186429930248</v>
+      </c>
+      <c r="F3">
+        <v>0.635997482693518</v>
+      </c>
+      <c r="G3">
+        <v>0.02435442418308652</v>
+      </c>
+      <c r="H3">
+        <v>0.7612016293279023</v>
+      </c>
+      <c r="I3">
+        <v>0.008655804480651732</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>0.501981351981352</v>
+      </c>
+      <c r="D4">
+        <v>0.498018648018648</v>
+      </c>
+      <c r="E4">
+        <v>0.2879923836724979</v>
+      </c>
+      <c r="F4">
+        <v>0.6636320643178056</v>
+      </c>
+      <c r="G4">
+        <v>0.03298752768387924</v>
+      </c>
+      <c r="H4">
+        <v>0.7673196368848543</v>
+      </c>
+      <c r="I4">
+        <v>0.008002866698518872</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>0.6226930963773069</v>
+      </c>
+      <c r="D5">
+        <v>0.3773069036226931</v>
+      </c>
+      <c r="E5">
+        <v>0.4955845990815966</v>
+      </c>
+      <c r="F5">
+        <v>0.5015728766165677</v>
+      </c>
+      <c r="G5">
+        <v>0.1015037593984962</v>
+      </c>
+      <c r="H5">
+        <v>0.7701841359773371</v>
+      </c>
+      <c r="I5">
+        <v>0.02939093484419263</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>0.4486048175530646</v>
+      </c>
+      <c r="D6">
+        <v>0.5513951824469354</v>
+      </c>
+      <c r="E6">
+        <v>0.4336023477622891</v>
+      </c>
+      <c r="F6">
+        <v>0.5585389453313981</v>
+      </c>
+      <c r="G6">
         <v>0.1194848557119008</v>
       </c>
-      <c r="H6" s="2">
-        <v>0.76333251413123615</v>
-      </c>
-      <c r="I6" s="2">
-        <v>3.8830179405259277E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="2">
-        <v>0.58667550546900893</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0.41332449453099113</v>
-      </c>
-      <c r="E7" s="2">
+      <c r="H6">
+        <v>0.7633325141312362</v>
+      </c>
+      <c r="I6">
+        <v>0.03883017940525928</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Hispan</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>0.5866755054690089</v>
+      </c>
+      <c r="D7">
+        <v>0.4133244945309911</v>
+      </c>
+      <c r="E7">
         <v>0.5027932960893855</v>
       </c>
-      <c r="F7" s="2">
-        <v>0.53180396246089678</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0.19489559164733181</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0.79411764705882348</v>
-      </c>
-      <c r="I7" s="2">
-        <v>6.3075832742735649E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0.42111999999999999</v>
-      </c>
-      <c r="D8" s="6">
-        <v>0.57887999999999995</v>
-      </c>
-      <c r="E8" s="6">
-        <v>0.44233964772349621</v>
-      </c>
-      <c r="F8" s="6">
+      <c r="F7">
+        <v>0.5318039624608968</v>
+      </c>
+      <c r="G7">
+        <v>0.1948955916473318</v>
+      </c>
+      <c r="H7">
+        <v>0.7941176470588235</v>
+      </c>
+      <c r="I7">
+        <v>0.06307583274273565</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Hispan</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>0.42112</v>
+      </c>
+      <c r="D8">
+        <v>0.57888</v>
+      </c>
+      <c r="E8">
+        <v>0.4423396477234962</v>
+      </c>
+      <c r="F8">
         <v>0.5384108143752061</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8">
         <v>0.19136</v>
       </c>
-      <c r="H8" s="6">
-        <v>0.79469976517946994</v>
-      </c>
-      <c r="I8" s="6">
-        <v>5.1325058705132508E-2</v>
+      <c r="H8">
+        <v>0.7946997651794699</v>
+      </c>
+      <c r="I8">
+        <v>0.05132505870513251</v>
       </c>
     </row>
   </sheetData>
